--- a/Estadistica-dasboard.xlsx
+++ b/Estadistica-dasboard.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jorge Borrero\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7226D9F9-D8F9-43F3-A77A-D0C0905183E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{125DFCEE-2417-4491-8B20-24A1EF285DF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F737A568-FD9A-4FA3-8F90-45341C9815F4}"/>
   </bookViews>
@@ -612,9 +612,8 @@
       <c r="B8" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="4" t="e">
-        <f>SKEW(#REF!)</f>
-        <v>#REF!</v>
+      <c r="C8" s="4">
+        <v>-1.6860394542014778E-2</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>20</v>
